--- a/www/download/IND.surplus_value.empe_hs.r.pc.EXI382.xlsx
+++ b/www/download/IND.surplus_value.empe_hs.r.pc.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -685,7 +690,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -697,7 +702,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -709,7 +714,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -721,7 +726,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -733,7 +738,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -745,7 +750,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -757,7 +762,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -769,7 +774,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -781,7 +786,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -793,7 +798,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -805,7 +810,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -817,7 +822,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -829,7 +834,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -841,7 +846,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -853,7 +858,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -865,7 +870,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -877,7 +882,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -889,7 +894,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -901,7 +906,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -913,7 +918,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -925,7 +930,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -937,7 +942,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -949,7 +954,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -961,7 +966,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -973,7 +978,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -985,7 +990,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -997,7 +1002,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1009,7 +1014,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1021,7 +1026,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1033,7 +1038,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1045,7 +1050,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1057,7 +1062,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1069,7 +1074,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1081,7 +1086,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1093,7 +1098,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1105,7 +1110,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1117,7 +1122,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1129,7 +1134,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1141,7 +1146,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1153,7 +1158,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1165,7 +1170,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1177,7 +1182,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1189,7 +1194,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1201,7 +1206,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1213,7 +1218,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1225,7 +1230,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1237,7 +1242,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1249,7 +1254,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1261,7 +1266,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1273,7 +1278,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1320,6 +1325,11 @@
           <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1354,6 +1364,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
